--- a/Cruce_HC_Octubre_vs_Matrices.xlsx
+++ b/Cruce_HC_Octubre_vs_Matrices.xlsx
@@ -15,9 +15,9 @@
     <sheet name="6. Trazabilidad" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1. Alcance y origen'!$A$4:$C$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1. Alcance y origen'!$A$4:$C$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2. Cruce por centro de costo'!$A$4:$G$84</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'3. Brechas'!$A$4:$E$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'3. Brechas'!$A$4:$E$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'4. Excluidos por alcance'!$A$4:$D$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'5. Cambios vs corte anterior'!$A$4:$C$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'6. Trazabilidad'!$A$4:$E$21</definedName>
@@ -524,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -656,17 +656,34 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
+          <t>Renombres validados</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>GE-SO-SF-D1 evalúa 'Medico Ocupacional' y 'Auxiliar de servicios de salud', que el head count de octubre denomina MEDICO y AUXILIAR DE SERVICIOS DE SALUD. Renombres confirmados por el responsable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
           <t>Verificación recomendada</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>Para un consolidado completo, con dotación por cargo y comparación automática contra el corte anterior, procesar el archivo Excel del head count con control_mensual.py.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:C10"/>
+  <autoFilter ref="A4:C11"/>
   <mergeCells count="2">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:C2"/>
@@ -1083,15 +1100,23 @@
           <t>AUXILIAR DE SERVICIOS DE SALUD</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>SIN ANALIZAR</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr"/>
-      <c r="E17" s="4" t="inlineStr"/>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>ANALIZADO</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>GE-SO-SF-D1</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Auxiliar de servicios de salud</t>
+        </is>
+      </c>
       <c r="F17" s="7" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G17" s="4" t="inlineStr"/>
     </row>
@@ -1141,17 +1166,29 @@
           <t>MEDICO</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>SIN ANALIZAR</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr"/>
-      <c r="E19" s="4" t="inlineStr"/>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>ANALIZADO</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>GE-SO-SF-D1</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Medico Ocupacional</t>
+        </is>
+      </c>
       <c r="F19" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="4" t="inlineStr"/>
+        <v>18</v>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>Denominación distinta en la matriz (equivalencia validada)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -3140,7 +3177,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -3232,12 +3269,12 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>4201 SALUD OCUPACIONAL</t>
+          <t>5800 GENERAL MANAGEMENT</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>AUXILIAR DE SERVICIOS DE SALUD</t>
+          <t>CHOFER</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -3251,12 +3288,12 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>5800 GENERAL MANAGEMENT</t>
+          <t>1200 PLANTATION MANAGEMENT</t>
         </is>
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>CHOFER</t>
+          <t>COORDINADOR DE SEGURIDAD FISICA</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -3270,12 +3307,12 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>1200 PLANTATION MANAGEMENT</t>
+          <t>5300 FINANCE</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>COORDINADOR DE SEGURIDAD FISICA</t>
+          <t>DIRECTOR FINANCIERO</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -3294,7 +3331,7 @@
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>DIRECTOR FINANCIERO</t>
+          <t>GERENTE FINANCIERO</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -3308,12 +3345,12 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>5300 FINANCE</t>
+          <t>5800 GENERAL MANAGEMENT</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>GERENTE FINANCIERO</t>
+          <t>GERENTE GENERAL</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -3327,12 +3364,12 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>5800 GENERAL MANAGEMENT</t>
+          <t>3120 PLANTA TERMICA PLANTABAL</t>
         </is>
       </c>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>GERENTE GENERAL</t>
+          <t>INGENIERO DE CALDERO</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -3346,12 +3383,12 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>3120 PLANTA TERMICA PLANTABAL</t>
+          <t>2500 SERVICE CENTER</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>INGENIERO DE CALDERO</t>
+          <t>JEFE DE BODEGA</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -3365,12 +3402,12 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>2500 SERVICE CENTER</t>
+          <t>5400 IT</t>
         </is>
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>JEFE DE BODEGA</t>
+          <t>JEFE DE DESARROLLO DE APLICACIONES</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -3384,12 +3421,12 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>5400 IT</t>
+          <t>5930 3ACM Expenses / 5934 BUSINESS CONTROLLER</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>JEFE DE DESARROLLO DE APLICACIONES</t>
+          <t>JUNIOR BUSINESS CONTROLLER</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -3403,12 +3440,12 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>5930 3ACM Expenses / 5934 BUSINESS CONTROLLER</t>
+          <t>5934 BUSINESS CONTROLLER</t>
         </is>
       </c>
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>JUNIOR BUSINESS CONTROLLER</t>
+          <t>SENIOR BUSINESS CONTROLLER</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -3422,12 +3459,12 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>4201 SALUD OCUPACIONAL</t>
+          <t>3010 KITS PRODUCTION - PGS / 3821 SUP DE PRODUCCION</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>MEDICO</t>
+          <t>SUPERVISOR DE PRODUCCIÓN</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -3438,46 +3475,8 @@
       <c r="D17" s="4" t="inlineStr"/>
       <c r="E17" s="4" t="inlineStr"/>
     </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>5934 BUSINESS CONTROLLER</t>
-        </is>
-      </c>
-      <c r="B18" s="12" t="inlineStr">
-        <is>
-          <t>SENIOR BUSINESS CONTROLLER</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>Elaborar matriz IPERC para el puesto</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>3010 KITS PRODUCTION - PGS / 3821 SUP DE PRODUCCION</t>
-        </is>
-      </c>
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t>SUPERVISOR DE PRODUCCIÓN</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>Elaborar matriz IPERC para el puesto</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr"/>
-      <c r="E19" s="4" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:E19"/>
+  <autoFilter ref="A4:E17"/>
   <mergeCells count="2">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
@@ -3712,7 +3711,7 @@
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="56" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -3776,7 +3775,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Evaluar si corresponde retirar su bloque de la matriz IPERC</t>
+          <t>Renombrado a MEDICO: sin accion</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3809,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Verificar cobertura</t>
+          <t>Ya cubierto por matriz</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3877,7 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Verificar cobertura</t>
+          <t>Ya cubierto por matriz</t>
         </is>
       </c>
     </row>

--- a/Cruce_HC_Octubre_vs_Matrices.xlsx
+++ b/Cruce_HC_Octubre_vs_Matrices.xlsx
@@ -11,16 +11,14 @@
     <sheet name="2. Cruce por centro de costo" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="3. Brechas" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="4. Excluidos por alcance" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="5. Cambios vs corte anterior" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="6. Trazabilidad" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="5. Trazabilidad" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1. Alcance y origen'!$A$4:$C$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2. Cruce por centro de costo'!$A$4:$G$84</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'3. Brechas'!$A$4:$E$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'4. Excluidos por alcance'!$A$4:$D$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'5. Cambios vs corte anterior'!$A$4:$C$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'6. Trazabilidad'!$A$4:$E$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1. Alcance y origen'!$A$4:$C$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2. Cruce por centro de costo'!$A$4:$G$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'3. Brechas'!$A$4:$E$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'4. Excluidos por alcance'!$A$4:$D$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'5. Trazabilidad'!$A$4:$E$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -147,10 +145,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -524,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -576,7 +574,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Transcripción de la tabla dinámica del head count de octubre de 2026, recibida como imagen. NO proviene del archivo Excel.</t>
+          <t>Transcripción de la tabla dinámica del head count (hc_tabla_octubre_2026.txt). NO proviene del archivo Excel.</t>
         </is>
       </c>
     </row>
@@ -656,34 +654,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Renombres validados</t>
+          <t>Verificación recomendada</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-SF-D1 evalúa 'Medico Ocupacional' y 'Auxiliar de servicios de salud', que el head count de octubre denomina MEDICO y AUXILIAR DE SERVICIOS DE SALUD. Renombres confirmados por el responsable.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Verificación recomendada</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
           <t>Para un consolidado completo, con dotación por cargo y comparación automática contra el corte anterior, procesar el archivo Excel del head count con control_mensual.py.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:C11"/>
+  <autoFilter ref="A4:C10"/>
   <mergeCells count="2">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:C2"/>
@@ -698,7 +679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G84"/>
+  <dimension ref="A1:G83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -713,7 +694,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CARGOS DEL HEAD COUNT DE OCTUBRE vs. MATRICES IPERC</t>
+          <t>CARGOS DEL HEAD COUNT vs. MATRICES IPERC</t>
         </is>
       </c>
     </row>
@@ -833,30 +814,38 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>3120 PLANTA TERMICA PLANTABAL</t>
+          <t>3158 PROYECTO W</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>INGENIERO DE CALDERO</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>SIN ANALIZAR</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr"/>
-      <c r="E8" s="5" t="inlineStr"/>
+          <t>AUXILIAR ADMINISTRATIVO</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>ANALIZADO</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>GE-SO-MA-D1 / GE-SO-RL-D35 / GE-SO-SF-D1</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Auxiliar Administrativo / Auxiliar administrativo / Auxiliar de servicios de salud</t>
+        </is>
+      </c>
       <c r="F8" s="8" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="G8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>3158 PROYECTO W</t>
+          <t>3251 PLANTABAL D100 #1</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -864,7 +853,7 @@
           <t>AUXILIAR ADMINISTRATIVO</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -887,43 +876,35 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>3251 PLANTABAL D100 #1</t>
+          <t>3801 PLANTABAL MANTENANCE #1</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>AUXILIAR ADMINISTRATIVO</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>ANALIZADO</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>GE-SO-MA-D1 / GE-SO-RL-D35 / GE-SO-SF-D1</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>Auxiliar Administrativo / Auxiliar administrativo / Auxiliar de servicios de salud</t>
-        </is>
-      </c>
+          <t>APRENDIZ</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>SIN ANALIZAR</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr"/>
+      <c r="E10" s="5" t="inlineStr"/>
       <c r="F10" s="8" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="G10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>3801 PLANTABAL MANTENANCE #1</t>
+          <t>3821 SUP DE PRODUCCION</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>APRENDIZ</t>
+          <t>SUPERVISOR DE PRODUCCIÓN</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -941,23 +922,31 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>3821 SUP DE PRODUCCION</t>
+          <t>4011 DISEÑO E INGENIERIA PGS</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>SUPERVISOR DE PRODUCCIÓN</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>SIN ANALIZAR</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="inlineStr"/>
+          <t>ANALISTA DE DISEÑO E INGENIERIA</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>ANALIZADO</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>GE-SO-PGS-D1</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Analista de Diseño e Ingenieria</t>
+        </is>
+      </c>
       <c r="F12" s="8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G12" s="5" t="inlineStr"/>
     </row>
@@ -969,10 +958,10 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>ANALISTA DE DISEÑO E INGENIERIA</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
+          <t>INGENIERO DE DISEÑO</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -984,48 +973,48 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Analista de Diseño e Ingenieria</t>
+          <t>Ingeniero de Diseño e Ingenieria</t>
         </is>
       </c>
       <c r="F13" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G13" s="4" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>Denominación distinta en la matriz (equivalencia validada)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>4011 DISEÑO E INGENIERIA PGS</t>
+          <t>4101 PLANTABAL MANUFACTURING #1</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>INGENIERO DE DISEÑO</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
+          <t>INGENIERO DE SEGURIDAD Y AMBIENTE</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-PGS-D1</t>
+          <t>GE-SO-EHS-D1</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>Ingeniero de Diseño e Ingenieria</t>
+          <t>Ingeniero de seguridad y ambiente</t>
         </is>
       </c>
       <c r="F14" s="8" t="n">
-        <v>14</v>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>Denominación distinta en la matriz (equivalencia validada)</t>
-        </is>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="G14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -1035,10 +1024,10 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>INGENIERO DE SEGURIDAD Y AMBIENTE</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
+          <t>TECNICO DE SEGURIDAD Y AMBIENTE</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -1050,42 +1039,42 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Ingeniero de seguridad y ambiente</t>
+          <t>Tecnico de seguridad y ambiente</t>
         </is>
       </c>
       <c r="F15" s="7" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>4101 PLANTABAL MANUFACTURING #1</t>
+          <t>4201 SALUD OCUPACIONAL</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>TECNICO DE SEGURIDAD Y AMBIENTE</t>
-        </is>
-      </c>
-      <c r="C16" s="10" t="inlineStr">
+          <t>AUXILIAR DE SERVICIOS DE SALUD</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-EHS-D1</t>
+          <t>GE-SO-SF-D1</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>Tecnico de seguridad y ambiente</t>
+          <t>Auxiliar de servicios de salud</t>
         </is>
       </c>
       <c r="F16" s="8" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G16" s="5" t="inlineStr"/>
     </row>
@@ -1097,10 +1086,10 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>AUXILIAR DE SERVICIOS DE SALUD</t>
-        </is>
-      </c>
-      <c r="C17" s="9" t="inlineStr">
+          <t>ENFERMERA/O</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -1112,13 +1101,17 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Auxiliar de servicios de salud</t>
+          <t>Enfermero Ocupacional</t>
         </is>
       </c>
       <c r="F17" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="G17" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>Denominación distinta en la matriz (equivalencia validada)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -1128,10 +1121,10 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>ENFERMERA/O</t>
-        </is>
-      </c>
-      <c r="C18" s="10" t="inlineStr">
+          <t>MEDICO</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -1143,11 +1136,11 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>Enfermero Ocupacional</t>
+          <t>Medico Ocupacional</t>
         </is>
       </c>
       <c r="F18" s="8" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
@@ -1158,37 +1151,33 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>4201 SALUD OCUPACIONAL</t>
+          <t>4203 SEGURIDAD OCUPACIONAL Y AMBIENTE</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>MEDICO</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
+          <t>INGENIERO DE SEGURIDAD Y AMBIENTE</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-SF-D1</t>
+          <t>GE-SO-EHS-D1</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Medico Ocupacional</t>
+          <t>Ingeniero de seguridad y ambiente</t>
         </is>
       </c>
       <c r="F19" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>Denominación distinta en la matriz (equivalencia validada)</t>
-        </is>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="G19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -1198,10 +1187,10 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>INGENIERO DE SEGURIDAD Y AMBIENTE</t>
-        </is>
-      </c>
-      <c r="C20" s="10" t="inlineStr">
+          <t>TECNICO DE SEGURIDAD Y AMBIENTE</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -1213,42 +1202,42 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>Ingeniero de seguridad y ambiente</t>
+          <t>Tecnico de seguridad y ambiente</t>
         </is>
       </c>
       <c r="F20" s="8" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>4203 SEGURIDAD OCUPACIONAL Y AMBIENTE</t>
+          <t>4300 PLANTABAL SCH</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>TECNICO DE SEGURIDAD Y AMBIENTE</t>
-        </is>
-      </c>
-      <c r="C21" s="9" t="inlineStr">
+          <t>ANALISTA DE SUPPLY CHAIN</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-EHS-D1</t>
+          <t>GE-SO-PO-D1 / GE-SO-SC-D1</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>Tecnico de seguridad y ambiente</t>
+          <t>Analista Supply Chain / Analista de Supply Chain</t>
         </is>
       </c>
       <c r="F21" s="7" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G21" s="4" t="inlineStr"/>
     </row>
@@ -1260,26 +1249,26 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>ANALISTA DE SUPPLY CHAIN</t>
-        </is>
-      </c>
-      <c r="C22" s="10" t="inlineStr">
+          <t>COORDINADOR DE SUPPLY CHAIN</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-PO-D1 / GE-SO-SC-D1</t>
+          <t>GE-SO-PO-D1</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>Analista Supply Chain / Analista de Supply Chain</t>
+          <t>Coordinador de Supply Chain</t>
         </is>
       </c>
       <c r="F22" s="8" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="G22" s="5" t="inlineStr"/>
     </row>
@@ -1291,10 +1280,10 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>COORDINADOR DE SUPPLY CHAIN</t>
-        </is>
-      </c>
-      <c r="C23" s="9" t="inlineStr">
+          <t>JEFE DE PLANIFICACION Y LOGISTICA</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -1306,11 +1295,11 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Coordinador de Supply Chain</t>
+          <t>Jefe de Planificación y Logística</t>
         </is>
       </c>
       <c r="F23" s="7" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G23" s="4" t="inlineStr"/>
     </row>
@@ -1322,10 +1311,10 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>JEFE DE PLANIFICACION Y LOGISTICA</t>
-        </is>
-      </c>
-      <c r="C24" s="10" t="inlineStr">
+          <t>PROGRAMADOR DE PRODUCCION</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -1337,42 +1326,42 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>Jefe de Planificación y Logística</t>
+          <t>Programador de Producción</t>
         </is>
       </c>
       <c r="F24" s="8" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G24" s="5" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>4300 PLANTABAL SCH</t>
+          <t>4350 CERTIFICACION FSC</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>PROGRAMADOR DE PRODUCCION</t>
-        </is>
-      </c>
-      <c r="C25" s="9" t="inlineStr">
+          <t>COORDINADORA DE CERTIFICACIONES</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-PO-D1</t>
+          <t>GE-SO-CE-D1</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Programador de Producción</t>
+          <t>Coordinador/a de Certificaciones</t>
         </is>
       </c>
       <c r="F25" s="7" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="G25" s="4" t="inlineStr"/>
     </row>
@@ -1384,10 +1373,10 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>COORDINADORA DE CERTIFICACIONES</t>
-        </is>
-      </c>
-      <c r="C26" s="10" t="inlineStr">
+          <t>ESPECIALISTA DE CERTIFICACIONES</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -1399,11 +1388,11 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>Coordinador/a de Certificaciones</t>
+          <t>Especialista de Certificaciones</t>
         </is>
       </c>
       <c r="F26" s="8" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G26" s="5" t="inlineStr"/>
     </row>
@@ -1415,10 +1404,10 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>ESPECIALISTA DE CERTIFICACIONES</t>
-        </is>
-      </c>
-      <c r="C27" s="9" t="inlineStr">
+          <t>TECNICO DE CERTIFICACIONES</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -1430,44 +1419,48 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>Especialista de Certificaciones</t>
+          <t>Técnico de Certificaciones</t>
         </is>
       </c>
       <c r="F27" s="7" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G27" s="4" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>4350 CERTIFICACION FSC</t>
+          <t>4400 PLANTABAL PURCHASE</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>TECNICO DE CERTIFICACIONES</t>
-        </is>
-      </c>
-      <c r="C28" s="10" t="inlineStr">
+          <t>ANALISTA DE COMPRAS</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-CE-D1</t>
+          <t>GE-SO-SC-D1</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>Técnico de Certificaciones</t>
+          <t>Analista Compras</t>
         </is>
       </c>
       <c r="F28" s="8" t="n">
-        <v>21</v>
-      </c>
-      <c r="G28" s="5" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>Denominación distinta en la matriz (equivalencia validada)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -1477,32 +1470,28 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>ANALISTA DE COMPRAS</t>
-        </is>
-      </c>
-      <c r="C29" s="9" t="inlineStr">
+          <t>ANALISTA DE SUPPLY CHAIN</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-SC-D1</t>
+          <t>GE-SO-PO-D1 / GE-SO-SC-D1</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>Analista Compras</t>
+          <t>Analista Supply Chain / Analista de Supply Chain</t>
         </is>
       </c>
       <c r="F29" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="G29" s="4" t="inlineStr">
-        <is>
-          <t>Denominación distinta en la matriz (equivalencia validada)</t>
-        </is>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="G29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -1512,63 +1501,63 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>ANALISTA DE SUPPLY CHAIN</t>
-        </is>
-      </c>
-      <c r="C30" s="10" t="inlineStr">
+          <t>JEFE DE COMPRAS E IMPORTACIONES</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-PO-D1 / GE-SO-SC-D1</t>
+          <t>GE-SO-SC-D1</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>Analista Supply Chain / Analista de Supply Chain</t>
+          <t>Jefe de Compras</t>
         </is>
       </c>
       <c r="F30" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="G30" s="5" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>Denominación distinta en la matriz (equivalencia validada)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>4400 PLANTABAL PURCHASE</t>
+          <t>4500 PLANTABAL QUALITY</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>JEFE DE COMPRAS E IMPORTACIONES</t>
-        </is>
-      </c>
-      <c r="C31" s="9" t="inlineStr">
+          <t>ANALISTA DE CALIDAD</t>
+        </is>
+      </c>
+      <c r="C31" s="10" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-SC-D1</t>
+          <t>GE-SO-CC-D1</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>Jefe de Compras</t>
+          <t>Analista de calidad</t>
         </is>
       </c>
       <c r="F31" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="G31" s="4" t="inlineStr">
-        <is>
-          <t>Denominación distinta en la matriz (equivalencia validada)</t>
-        </is>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="G31" s="4" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -1578,10 +1567,10 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>ANALISTA DE CALIDAD</t>
-        </is>
-      </c>
-      <c r="C32" s="10" t="inlineStr">
+          <t>COORDINADOR DE CALIDAD</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -1593,7 +1582,7 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>Analista de calidad</t>
+          <t>Coordinador de calidad</t>
         </is>
       </c>
       <c r="F32" s="8" t="n">
@@ -1609,10 +1598,10 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>COORDINADOR DE CALIDAD</t>
-        </is>
-      </c>
-      <c r="C33" s="9" t="inlineStr">
+          <t>GERENTE DE CALIDAD Y CERTIFICACIONES</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -1624,13 +1613,17 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>Coordinador de calidad</t>
+          <t>QSE &amp; Operational Excellence Manager</t>
         </is>
       </c>
       <c r="F33" s="7" t="n">
-        <v>57</v>
-      </c>
-      <c r="G33" s="4" t="inlineStr"/>
+        <v>23</v>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>Denominación distinta en la matriz (equivalencia validada)</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -1640,10 +1633,10 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>GERENTE DE CALIDAD Y CERTIFICACIONES</t>
-        </is>
-      </c>
-      <c r="C34" s="10" t="inlineStr">
+          <t>TECNICO DE CALIDAD</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -1655,46 +1648,42 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>QSE &amp; Operational Excellence Manager</t>
+          <t>Técnico de calidad</t>
         </is>
       </c>
       <c r="F34" s="8" t="n">
-        <v>23</v>
-      </c>
-      <c r="G34" s="5" t="inlineStr">
-        <is>
-          <t>Denominación distinta en la matriz (equivalencia validada)</t>
-        </is>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="G34" s="5" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>4500 PLANTABAL QUALITY</t>
+          <t>4600 PROYECTOS</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>TECNICO DE CALIDAD</t>
-        </is>
-      </c>
-      <c r="C35" s="9" t="inlineStr">
+          <t>ANALISTA DE PROYECTOS</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-CC-D1</t>
+          <t>GE-SO-PY-D1</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>Técnico de calidad</t>
+          <t>Analista de Proyectos</t>
         </is>
       </c>
       <c r="F35" s="7" t="n">
-        <v>58</v>
+        <v>16</v>
       </c>
       <c r="G35" s="4" t="inlineStr"/>
     </row>
@@ -1706,10 +1695,10 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>ANALISTA DE PROYECTOS</t>
-        </is>
-      </c>
-      <c r="C36" s="10" t="inlineStr">
+          <t>INGENIERO DE PROYECTOS</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -1721,11 +1710,11 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>Analista de Proyectos</t>
+          <t>Ingeniero de Proyectos</t>
         </is>
       </c>
       <c r="F36" s="8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G36" s="5" t="inlineStr"/>
     </row>
@@ -1737,10 +1726,10 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>INGENIERO DE PROYECTOS</t>
-        </is>
-      </c>
-      <c r="C37" s="9" t="inlineStr">
+          <t>JEFE DE PROYECTOS</t>
+        </is>
+      </c>
+      <c r="C37" s="10" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -1752,73 +1741,73 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>Ingeniero de Proyectos</t>
+          <t>Jefe de Proyectos</t>
         </is>
       </c>
       <c r="F37" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G37" s="4" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>4600 PROYECTOS</t>
+          <t>4650 EXCELENCIA OPERACIONAL</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>JEFE DE PROYECTOS</t>
-        </is>
-      </c>
-      <c r="C38" s="10" t="inlineStr">
+          <t>COORDINADOR DE EXCELENCIA OPERACIONAL</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-PY-D1</t>
+          <t>GE-SO-EO-D1</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>Jefe de Proyectos</t>
+          <t>Coordinador de Excelencia Operacional</t>
         </is>
       </c>
       <c r="F38" s="8" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G38" s="5" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>4650 EXCELENCIA OPERACIONAL</t>
+          <t>4800 PLANTABAL OPERATIONS MNG STAFF</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>COORDINADOR DE EXCELENCIA OPERACIONAL</t>
-        </is>
-      </c>
-      <c r="C39" s="9" t="inlineStr">
+          <t>AUXILIAR ADMINISTRATIVO</t>
+        </is>
+      </c>
+      <c r="C39" s="10" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-EO-D1</t>
+          <t>GE-SO-MA-D1 / GE-SO-RL-D35 / GE-SO-SF-D1</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>Coordinador de Excelencia Operacional</t>
+          <t>Auxiliar Administrativo / Auxiliar administrativo / Auxiliar de servicios de salud</t>
         </is>
       </c>
       <c r="F39" s="7" t="n">
-        <v>12</v>
+        <v>58</v>
       </c>
       <c r="G39" s="4" t="inlineStr"/>
     </row>
@@ -1830,26 +1819,26 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>AUXILIAR ADMINISTRATIVO</t>
-        </is>
-      </c>
-      <c r="C40" s="10" t="inlineStr">
+          <t>DIRECTOR DE OPERACIONES</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-MA-D1 / GE-SO-RL-D35 / GE-SO-SF-D1</t>
+          <t>GE-SO-RL-D35</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>Auxiliar Administrativo / Auxiliar administrativo / Auxiliar de servicios de salud</t>
+          <t>Director de Operaciones</t>
         </is>
       </c>
       <c r="F40" s="8" t="n">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G40" s="5" t="inlineStr"/>
     </row>
@@ -1861,10 +1850,10 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>DIRECTOR DE OPERACIONES</t>
-        </is>
-      </c>
-      <c r="C41" s="9" t="inlineStr">
+          <t>GERENTE DE PRODUCCION</t>
+        </is>
+      </c>
+      <c r="C41" s="10" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -1876,11 +1865,11 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>Director de Operaciones</t>
+          <t>Gerente de Producción</t>
         </is>
       </c>
       <c r="F41" s="7" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G41" s="4" t="inlineStr"/>
     </row>
@@ -1892,10 +1881,10 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>GERENTE DE PRODUCCION</t>
-        </is>
-      </c>
-      <c r="C42" s="10" t="inlineStr">
+          <t>JEFE DE PRODUCCION</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -1907,48 +1896,48 @@
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>Gerente de Producción</t>
+          <t>Jefe de Producción (MV y Secado)</t>
         </is>
       </c>
       <c r="F42" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="G42" s="5" t="inlineStr"/>
+        <v>18</v>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>Denominación distinta en la matriz (equivalencia validada)</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>4800 PLANTABAL OPERATIONS MNG STAFF</t>
+          <t>4807 MANAGEMENT STAFF</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>JEFE DE PRODUCCION</t>
-        </is>
-      </c>
-      <c r="C43" s="9" t="inlineStr">
+          <t>AUXILIAR ADMINISTRATIVO</t>
+        </is>
+      </c>
+      <c r="C43" s="10" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-RL-D35</t>
+          <t>GE-SO-MA-D1 / GE-SO-RL-D35 / GE-SO-SF-D1</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>Jefe de Producción (MV y Secado)</t>
+          <t>Auxiliar Administrativo / Auxiliar administrativo / Auxiliar de servicios de salud</t>
         </is>
       </c>
       <c r="F43" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="G43" s="4" t="inlineStr">
-        <is>
-          <t>Denominación distinta en la matriz (equivalencia validada)</t>
-        </is>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="G43" s="4" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -1958,63 +1947,63 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>AUXILIAR ADMINISTRATIVO</t>
-        </is>
-      </c>
-      <c r="C44" s="10" t="inlineStr">
+          <t>JEFE DE PRODUCCION</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-MA-D1 / GE-SO-RL-D35 / GE-SO-SF-D1</t>
+          <t>GE-SO-RL-D35</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>Auxiliar Administrativo / Auxiliar administrativo / Auxiliar de servicios de salud</t>
+          <t>Jefe de Producción (MV y Secado)</t>
         </is>
       </c>
       <c r="F44" s="8" t="n">
-        <v>58</v>
-      </c>
-      <c r="G44" s="5" t="inlineStr"/>
+        <v>18</v>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>Denominación distinta en la matriz (equivalencia validada)</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>4807 MANAGEMENT STAFF</t>
+          <t>4808 MAINTENANCE MNG STAFF</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>JEFE DE PRODUCCION</t>
-        </is>
-      </c>
-      <c r="C45" s="9" t="inlineStr">
+          <t>AUXILIAR ADMINISTRATIVO</t>
+        </is>
+      </c>
+      <c r="C45" s="10" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-RL-D35</t>
+          <t>GE-SO-MA-D1 / GE-SO-RL-D35 / GE-SO-SF-D1</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>Jefe de Producción (MV y Secado)</t>
+          <t>Auxiliar Administrativo / Auxiliar administrativo / Auxiliar de servicios de salud</t>
         </is>
       </c>
       <c r="F45" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="G45" s="4" t="inlineStr">
-        <is>
-          <t>Denominación distinta en la matriz (equivalencia validada)</t>
-        </is>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="G45" s="4" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
@@ -2024,26 +2013,26 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>AUXILIAR ADMINISTRATIVO</t>
-        </is>
-      </c>
-      <c r="C46" s="10" t="inlineStr">
+          <t>GERENTE JR DE MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-MA-D1 / GE-SO-RL-D35 / GE-SO-SF-D1</t>
+          <t>GE-SO-MA-D1</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>Auxiliar Administrativo / Auxiliar administrativo / Auxiliar de servicios de salud</t>
+          <t>Gerente JR de mantenimiento</t>
         </is>
       </c>
       <c r="F46" s="8" t="n">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="G46" s="5" t="inlineStr"/>
     </row>
@@ -2055,10 +2044,10 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>GERENTE JR DE MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="C47" s="9" t="inlineStr">
+          <t>JEFE DE MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="C47" s="10" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -2070,11 +2059,11 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>Gerente JR de mantenimiento</t>
+          <t>Jefe de mantenimiento</t>
         </is>
       </c>
       <c r="F47" s="7" t="n">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="G47" s="4" t="inlineStr"/>
     </row>
@@ -2086,10 +2075,10 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>JEFE DE MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="C48" s="10" t="inlineStr">
+          <t>PLANIFICADOR DE MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -2101,11 +2090,11 @@
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>Jefe de mantenimiento</t>
+          <t>Planificador de mantenimiento</t>
         </is>
       </c>
       <c r="F48" s="8" t="n">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="G48" s="5" t="inlineStr"/>
     </row>
@@ -2117,10 +2106,10 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>PLANIFICADOR DE MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="C49" s="9" t="inlineStr">
+          <t>SUPERVISOR DE MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="C49" s="10" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -2132,42 +2121,42 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>Planificador de mantenimiento</t>
+          <t>Supervisor de mantenimiento</t>
         </is>
       </c>
       <c r="F49" s="7" t="n">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="G49" s="4" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>4808 MAINTENANCE MNG STAFF</t>
+          <t>4950 INVENTARY</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>SUPERVISOR DE MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="C50" s="10" t="inlineStr">
+          <t>ANALISTA DE INVENTARIO</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-MA-D1</t>
+          <t>GE-SO-CI-D1</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>Supervisor de mantenimiento</t>
+          <t>Analista de Inventario</t>
         </is>
       </c>
       <c r="F50" s="8" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="G50" s="5" t="inlineStr"/>
     </row>
@@ -2179,10 +2168,10 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>ANALISTA DE INVENTARIO</t>
-        </is>
-      </c>
-      <c r="C51" s="9" t="inlineStr">
+          <t>TECNICO DE INVENTARIO</t>
+        </is>
+      </c>
+      <c r="C51" s="10" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -2194,69 +2183,69 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>Analista de Inventario</t>
+          <t>Técnico de Inventario</t>
         </is>
       </c>
       <c r="F51" s="7" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G51" s="4" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>4950 INVENTARY</t>
+          <t>5001 PGS-CMBA-FINANCE</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>TECNICO DE INVENTARIO</t>
-        </is>
-      </c>
-      <c r="C52" s="10" t="inlineStr">
+          <t>JEFE DE CONTABILIDAD E IMPUESTOS</t>
+        </is>
+      </c>
+      <c r="C52" s="9" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-CI-D1</t>
+          <t>GE-SO-FI-D1</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>Técnico de Inventario</t>
+          <t>Jefe de Contabilidad e Impuestos</t>
         </is>
       </c>
       <c r="F52" s="8" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G52" s="5" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>5001 PGS-CMBA-FINANCE</t>
+          <t>5006 PGS-ENGICORE AMERICAS</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>JEFE DE CONTABILIDAD E IMPUESTOS</t>
-        </is>
-      </c>
-      <c r="C53" s="9" t="inlineStr">
+          <t>JEFE DE DISEÑO E INGENIERIA</t>
+        </is>
+      </c>
+      <c r="C53" s="10" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-FI-D1</t>
+          <t>GE-SO-PGS-D1</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>Jefe de Contabilidad e Impuestos</t>
+          <t>Jefe de Diseño e Ingenieria</t>
         </is>
       </c>
       <c r="F53" s="7" t="n">
@@ -2267,27 +2256,27 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>5006 PGS-ENGICORE AMERICAS</t>
+          <t>5210 LABORATORIO DE BALSA</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>JEFE DE DISEÑO E INGENIERIA</t>
-        </is>
-      </c>
-      <c r="C54" s="10" t="inlineStr">
+          <t>SUPERVISOR DE LABORATORIO</t>
+        </is>
+      </c>
+      <c r="C54" s="9" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-PGS-D1</t>
+          <t>GE-SO-BL-D1</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>Jefe de Diseño e Ingenieria</t>
+          <t>Supervisor de Laboratorio</t>
         </is>
       </c>
       <c r="F54" s="8" t="n">
@@ -2303,10 +2292,10 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>SUPERVISOR DE LABORATORIO</t>
-        </is>
-      </c>
-      <c r="C55" s="9" t="inlineStr">
+          <t>TECNICO DE LABORATORIO</t>
+        </is>
+      </c>
+      <c r="C55" s="10" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -2318,7 +2307,7 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>Supervisor de Laboratorio</t>
+          <t>Técnico de Laboratorio</t>
         </is>
       </c>
       <c r="F55" s="7" t="n">
@@ -2329,31 +2318,23 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>5210 LABORATORIO DE BALSA</t>
+          <t>5300 FINANCE</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>TECNICO DE LABORATORIO</t>
-        </is>
-      </c>
-      <c r="C56" s="10" t="inlineStr">
-        <is>
-          <t>ANALIZADO</t>
-        </is>
-      </c>
-      <c r="D56" s="5" t="inlineStr">
-        <is>
-          <t>GE-SO-BL-D1</t>
-        </is>
-      </c>
-      <c r="E56" s="5" t="inlineStr">
-        <is>
-          <t>Técnico de Laboratorio</t>
-        </is>
-      </c>
+          <t>ANALISTA DE IMPUESTOS</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>SIN ANALIZAR</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr"/>
+      <c r="E56" s="5" t="inlineStr"/>
       <c r="F56" s="8" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G56" s="5" t="inlineStr"/>
     </row>
@@ -2365,18 +2346,26 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>ANALISTA DE IMPUESTOS</t>
-        </is>
-      </c>
-      <c r="C57" s="6" t="inlineStr">
-        <is>
-          <t>SIN ANALIZAR</t>
-        </is>
-      </c>
-      <c r="D57" s="4" t="inlineStr"/>
-      <c r="E57" s="4" t="inlineStr"/>
+          <t>ANALISTA FINANCIERO</t>
+        </is>
+      </c>
+      <c r="C57" s="10" t="inlineStr">
+        <is>
+          <t>ANALIZADO</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>GE-SO-FI-D1</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>Analista financiero</t>
+        </is>
+      </c>
       <c r="F57" s="7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G57" s="4" t="inlineStr"/>
     </row>
@@ -2388,10 +2377,10 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>ANALISTA FINANCIERO</t>
-        </is>
-      </c>
-      <c r="C58" s="10" t="inlineStr">
+          <t>COORDINADOR CONTABLE</t>
+        </is>
+      </c>
+      <c r="C58" s="9" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -2403,11 +2392,11 @@
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>Analista financiero</t>
+          <t>Coordinador Contable</t>
         </is>
       </c>
       <c r="F58" s="8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G58" s="5" t="inlineStr"/>
     </row>
@@ -2419,10 +2408,10 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>COORDINADOR CONTABLE</t>
-        </is>
-      </c>
-      <c r="C59" s="9" t="inlineStr">
+          <t>COORDINADOR CONTABLE Y DE IMPUESTOS</t>
+        </is>
+      </c>
+      <c r="C59" s="10" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -2434,11 +2423,11 @@
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>Coordinador Contable</t>
+          <t>Coordinador Contable y de Impuestos</t>
         </is>
       </c>
       <c r="F59" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G59" s="4" t="inlineStr"/>
     </row>
@@ -2450,26 +2439,18 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>COORDINADOR CONTABLE Y DE IMPUESTOS</t>
-        </is>
-      </c>
-      <c r="C60" s="10" t="inlineStr">
-        <is>
-          <t>ANALIZADO</t>
-        </is>
-      </c>
-      <c r="D60" s="5" t="inlineStr">
-        <is>
-          <t>GE-SO-FI-D1</t>
-        </is>
-      </c>
-      <c r="E60" s="5" t="inlineStr">
-        <is>
-          <t>Coordinador Contable y de Impuestos</t>
-        </is>
-      </c>
+          <t>DIRECTOR FINANCIERO</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>SIN ANALIZAR</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr"/>
+      <c r="E60" s="5" t="inlineStr"/>
       <c r="F60" s="8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G60" s="5" t="inlineStr"/>
     </row>
@@ -2481,7 +2462,7 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>DIRECTOR FINANCIERO</t>
+          <t>GERENTE FINANCIERO</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
@@ -2499,25 +2480,37 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>5300 FINANCE</t>
+          <t>5400 IT</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>GERENTE FINANCIERO</t>
-        </is>
-      </c>
-      <c r="C62" s="6" t="inlineStr">
-        <is>
-          <t>SIN ANALIZAR</t>
-        </is>
-      </c>
-      <c r="D62" s="5" t="inlineStr"/>
-      <c r="E62" s="5" t="inlineStr"/>
+          <t>ASISTENTE DE DESARROLLO DE SISTEMA</t>
+        </is>
+      </c>
+      <c r="C62" s="9" t="inlineStr">
+        <is>
+          <t>ANALIZADO</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>GE-SO-IT-D1</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="inlineStr">
+        <is>
+          <t>Analista de desarrollo y sistema</t>
+        </is>
+      </c>
       <c r="F62" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G62" s="5" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="G62" s="5" t="inlineStr">
+        <is>
+          <t>Denominación distinta en la matriz (equivalencia validada)</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
@@ -2527,10 +2520,10 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>ASISTENTE DE DESARROLLO DE SISTEMA</t>
-        </is>
-      </c>
-      <c r="C63" s="9" t="inlineStr">
+          <t>DESARROLLADOR JR</t>
+        </is>
+      </c>
+      <c r="C63" s="10" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -2542,17 +2535,13 @@
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>Analista de desarrollo y sistema</t>
+          <t>Desarrollador JR</t>
         </is>
       </c>
       <c r="F63" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="G63" s="4" t="inlineStr">
-        <is>
-          <t>Denominación distinta en la matriz (equivalencia validada)</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="G63" s="4" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
@@ -2562,10 +2551,10 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>DESARROLLADOR JR</t>
-        </is>
-      </c>
-      <c r="C64" s="10" t="inlineStr">
+          <t>HELP DESK</t>
+        </is>
+      </c>
+      <c r="C64" s="9" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -2577,11 +2566,11 @@
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>Desarrollador JR</t>
+          <t>Help Desk</t>
         </is>
       </c>
       <c r="F64" s="8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G64" s="5" t="inlineStr"/>
     </row>
@@ -2593,26 +2582,18 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>HELP DESK</t>
-        </is>
-      </c>
-      <c r="C65" s="9" t="inlineStr">
-        <is>
-          <t>ANALIZADO</t>
-        </is>
-      </c>
-      <c r="D65" s="4" t="inlineStr">
-        <is>
-          <t>GE-SO-IT-D1</t>
-        </is>
-      </c>
-      <c r="E65" s="4" t="inlineStr">
-        <is>
-          <t>Help Desk</t>
-        </is>
-      </c>
+          <t>JEFE DE DESARROLLO DE APLICACIONES</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>SIN ANALIZAR</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr"/>
+      <c r="E65" s="4" t="inlineStr"/>
       <c r="F65" s="7" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G65" s="4" t="inlineStr"/>
     </row>
@@ -2624,55 +2605,63 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>JEFE DE DESARROLLO DE APLICACIONES</t>
-        </is>
-      </c>
-      <c r="C66" s="6" t="inlineStr">
-        <is>
-          <t>SIN ANALIZAR</t>
-        </is>
-      </c>
-      <c r="D66" s="5" t="inlineStr"/>
-      <c r="E66" s="5" t="inlineStr"/>
+          <t>REGIONAL IT MANAGER</t>
+        </is>
+      </c>
+      <c r="C66" s="9" t="inlineStr">
+        <is>
+          <t>ANALIZADO</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>GE-SO-IT-D1</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
+          <t>Gerente tecnologico</t>
+        </is>
+      </c>
       <c r="F66" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G66" s="5" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="G66" s="5" t="inlineStr">
+        <is>
+          <t>Denominación distinta en la matriz (equivalencia validada)</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>5400 IT</t>
+          <t>5500 HR</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>REGIONAL IT MANAGER</t>
-        </is>
-      </c>
-      <c r="C67" s="9" t="inlineStr">
+          <t>ANALISTA DE DESARROLLO ORGANIZACIONAL</t>
+        </is>
+      </c>
+      <c r="C67" s="10" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-IT-D1</t>
+          <t>GE-SO-TH-D1</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>Gerente tecnologico</t>
+          <t>ANALISTA DE DESARROLLO ORGANIZACIONAL</t>
         </is>
       </c>
       <c r="F67" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="G67" s="4" t="inlineStr">
-        <is>
-          <t>Denominación distinta en la matriz (equivalencia validada)</t>
-        </is>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="G67" s="4" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
@@ -2682,10 +2671,10 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>ANALISTA DE DESARROLLO ORGANIZACIONAL</t>
-        </is>
-      </c>
-      <c r="C68" s="10" t="inlineStr">
+          <t>ANALISTA DE RECURSOS HUMANOS</t>
+        </is>
+      </c>
+      <c r="C68" s="9" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -2697,11 +2686,11 @@
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>ANALISTA DE DESARROLLO ORGANIZACIONAL</t>
+          <t>ANALISTA DE RECURSOS HUMANOS</t>
         </is>
       </c>
       <c r="F68" s="8" t="n">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="G68" s="5" t="inlineStr"/>
     </row>
@@ -2713,10 +2702,10 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>ANALISTA DE RECURSOS HUMANOS</t>
-        </is>
-      </c>
-      <c r="C69" s="9" t="inlineStr">
+          <t>ANALISTA DE RECURSOS HUMANOS Y NOMINA</t>
+        </is>
+      </c>
+      <c r="C69" s="10" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -2728,11 +2717,11 @@
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>ANALISTA DE RECURSOS HUMANOS</t>
+          <t>ANALISTA DE RECURSOS HUMANOS Y NÓMINA</t>
         </is>
       </c>
       <c r="F69" s="7" t="n">
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="G69" s="4" t="inlineStr"/>
     </row>
@@ -2744,10 +2733,10 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>ANALISTA DE RECURSOS HUMANOS Y NOMINA</t>
-        </is>
-      </c>
-      <c r="C70" s="10" t="inlineStr">
+          <t>BUSINESS PARTNER DE RECURSOS HUMANOS</t>
+        </is>
+      </c>
+      <c r="C70" s="9" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -2759,7 +2748,7 @@
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>ANALISTA DE RECURSOS HUMANOS Y NÓMINA</t>
+          <t>BUSINNES PARTNER DE RECURSOS HUMANOS</t>
         </is>
       </c>
       <c r="F70" s="8" t="n">
@@ -2775,10 +2764,10 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>BUSINESS PARTNER DE RECURSOS HUMANOS</t>
-        </is>
-      </c>
-      <c r="C71" s="9" t="inlineStr">
+          <t>COORDINADORA DE DESARROLLO ORGANIZACIONAL</t>
+        </is>
+      </c>
+      <c r="C71" s="10" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -2790,11 +2779,11 @@
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>BUSINNES PARTNER DE RECURSOS HUMANOS</t>
+          <t>COORDINADORA DE DESARROLLO ORGANIZACIONAL</t>
         </is>
       </c>
       <c r="F71" s="7" t="n">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="G71" s="4" t="inlineStr"/>
     </row>
@@ -2806,10 +2795,10 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>COORDINADORA DE DESARROLLO ORGANIZACIONAL</t>
-        </is>
-      </c>
-      <c r="C72" s="10" t="inlineStr">
+          <t>HR BUSINESS PARTNER AMERICAS</t>
+        </is>
+      </c>
+      <c r="C72" s="9" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -2821,11 +2810,11 @@
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>COORDINADORA DE DESARROLLO ORGANIZACIONAL</t>
+          <t>HR BUSINNES PARTNER AMERICAS</t>
         </is>
       </c>
       <c r="F72" s="8" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="G72" s="5" t="inlineStr"/>
     </row>
@@ -2837,10 +2826,10 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>HR BUSINESS PARTNER AMERICAS</t>
-        </is>
-      </c>
-      <c r="C73" s="9" t="inlineStr">
+          <t>PEOPLE OPERATIONS PARTNER</t>
+        </is>
+      </c>
+      <c r="C73" s="10" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -2852,7 +2841,7 @@
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>HR BUSINNES PARTNER AMERICAS</t>
+          <t>PEOPLE OPERATIONS PARTNER</t>
         </is>
       </c>
       <c r="F73" s="7" t="n">
@@ -2863,31 +2852,31 @@
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>5500 HR</t>
+          <t>5600 LEGAL</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>PEOPLE OPERATIONS PARTNER</t>
-        </is>
-      </c>
-      <c r="C74" s="10" t="inlineStr">
+          <t>ANALISTA LEGAL</t>
+        </is>
+      </c>
+      <c r="C74" s="9" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-TH-D1</t>
+          <t>GE-SO-LE-D1</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>PEOPLE OPERATIONS PARTNER</t>
+          <t>Analista Legal</t>
         </is>
       </c>
       <c r="F74" s="8" t="n">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="G74" s="5" t="inlineStr"/>
     </row>
@@ -2899,10 +2888,10 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>ANALISTA LEGAL</t>
-        </is>
-      </c>
-      <c r="C75" s="9" t="inlineStr">
+          <t>ASISTENTE LEGAL</t>
+        </is>
+      </c>
+      <c r="C75" s="10" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -2914,11 +2903,11 @@
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>Analista Legal</t>
+          <t>Asistente Legal</t>
         </is>
       </c>
       <c r="F75" s="7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G75" s="4" t="inlineStr"/>
     </row>
@@ -2930,10 +2919,10 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>ASISTENTE LEGAL</t>
-        </is>
-      </c>
-      <c r="C76" s="10" t="inlineStr">
+          <t>COORDINADOR DE ASUNTOS LEGALES</t>
+        </is>
+      </c>
+      <c r="C76" s="9" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -2945,73 +2934,65 @@
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>Asistente Legal</t>
+          <t>Coordinador/a de Asuntos Legales</t>
         </is>
       </c>
       <c r="F76" s="8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G76" s="5" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>5600 LEGAL</t>
+          <t>5700 ADMINISTRACION</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>COORDINADOR DE ASUNTOS LEGALES</t>
-        </is>
-      </c>
-      <c r="C77" s="9" t="inlineStr">
+          <t>HR DIRECTOR AMERICAS</t>
+        </is>
+      </c>
+      <c r="C77" s="10" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-LE-D1</t>
+          <t>GE-SO-TH-D1</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>Coordinador/a de Asuntos Legales</t>
+          <t>HR DIRECTOR AMERICAS</t>
         </is>
       </c>
       <c r="F77" s="7" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="G77" s="4" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>5700 ADMINISTRACION</t>
+          <t>5800 GENERAL MANAGEMENT</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>HR DIRECTOR AMERICAS</t>
-        </is>
-      </c>
-      <c r="C78" s="10" t="inlineStr">
-        <is>
-          <t>ANALIZADO</t>
-        </is>
-      </c>
-      <c r="D78" s="5" t="inlineStr">
-        <is>
-          <t>GE-SO-TH-D1</t>
-        </is>
-      </c>
-      <c r="E78" s="5" t="inlineStr">
-        <is>
-          <t>HR DIRECTOR AMERICAS</t>
-        </is>
-      </c>
+          <t>CHOFER</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>SIN ANALIZAR</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="inlineStr"/>
+      <c r="E78" s="5" t="inlineStr"/>
       <c r="F78" s="8" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="G78" s="5" t="inlineStr"/>
     </row>
@@ -3023,7 +3004,7 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>CHOFER</t>
+          <t>GERENTE GENERAL</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
@@ -3041,61 +3022,61 @@
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>5800 GENERAL MANAGEMENT</t>
+          <t>5918 PGS</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>GERENTE GENERAL</t>
-        </is>
-      </c>
-      <c r="C80" s="6" t="inlineStr">
-        <is>
-          <t>SIN ANALIZAR</t>
-        </is>
-      </c>
-      <c r="D80" s="5" t="inlineStr"/>
-      <c r="E80" s="5" t="inlineStr"/>
+          <t>AUXILIAR ADMINISTRATIVO</t>
+        </is>
+      </c>
+      <c r="C80" s="9" t="inlineStr">
+        <is>
+          <t>ANALIZADO</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="inlineStr">
+        <is>
+          <t>GE-SO-MA-D1 / GE-SO-RL-D35 / GE-SO-SF-D1</t>
+        </is>
+      </c>
+      <c r="E80" s="5" t="inlineStr">
+        <is>
+          <t>Auxiliar Administrativo / Auxiliar administrativo / Auxiliar de servicios de salud</t>
+        </is>
+      </c>
       <c r="F80" s="8" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="G80" s="5" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>5918 PGS</t>
+          <t>5930 3ACM Expenses</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>AUXILIAR ADMINISTRATIVO</t>
-        </is>
-      </c>
-      <c r="C81" s="9" t="inlineStr">
-        <is>
-          <t>ANALIZADO</t>
-        </is>
-      </c>
-      <c r="D81" s="4" t="inlineStr">
-        <is>
-          <t>GE-SO-MA-D1 / GE-SO-RL-D35 / GE-SO-SF-D1</t>
-        </is>
-      </c>
-      <c r="E81" s="4" t="inlineStr">
-        <is>
-          <t>Auxiliar Administrativo / Auxiliar administrativo / Auxiliar de servicios de salud</t>
-        </is>
-      </c>
+          <t>JUNIOR BUSINESS CONTROLLER</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>SIN ANALIZAR</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="inlineStr"/>
+      <c r="E81" s="4" t="inlineStr"/>
       <c r="F81" s="7" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="G81" s="4" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>5930 3ACM Expenses</t>
+          <t>5934 BUSINESS CONTROLLER</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
@@ -3123,7 +3104,7 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>JUNIOR BUSINESS CONTROLLER</t>
+          <t>SENIOR BUSINESS CONTROLLER</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
@@ -3138,31 +3119,8 @@
       </c>
       <c r="G83" s="4" t="inlineStr"/>
     </row>
-    <row r="84">
-      <c r="A84" s="5" t="inlineStr">
-        <is>
-          <t>5934 BUSINESS CONTROLLER</t>
-        </is>
-      </c>
-      <c r="B84" s="5" t="inlineStr">
-        <is>
-          <t>SENIOR BUSINESS CONTROLLER</t>
-        </is>
-      </c>
-      <c r="C84" s="6" t="inlineStr">
-        <is>
-          <t>SIN ANALIZAR</t>
-        </is>
-      </c>
-      <c r="D84" s="5" t="inlineStr"/>
-      <c r="E84" s="5" t="inlineStr"/>
-      <c r="F84" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G84" s="5" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:G84"/>
+  <autoFilter ref="A4:G83"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
@@ -3177,7 +3135,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -3364,12 +3322,12 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>3120 PLANTA TERMICA PLANTABAL</t>
+          <t>2500 SERVICE CENTER</t>
         </is>
       </c>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>INGENIERO DE CALDERO</t>
+          <t>JEFE DE BODEGA</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -3383,12 +3341,12 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2500 SERVICE CENTER</t>
+          <t>5400 IT</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>JEFE DE BODEGA</t>
+          <t>JEFE DE DESARROLLO DE APLICACIONES</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -3402,12 +3360,12 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>5400 IT</t>
+          <t>5930 3ACM Expenses / 5934 BUSINESS CONTROLLER</t>
         </is>
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>JEFE DE DESARROLLO DE APLICACIONES</t>
+          <t>JUNIOR BUSINESS CONTROLLER</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -3421,12 +3379,12 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>5930 3ACM Expenses / 5934 BUSINESS CONTROLLER</t>
+          <t>5934 BUSINESS CONTROLLER</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>JUNIOR BUSINESS CONTROLLER</t>
+          <t>SENIOR BUSINESS CONTROLLER</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -3440,12 +3398,12 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>5934 BUSINESS CONTROLLER</t>
+          <t>3010 KITS PRODUCTION - PGS / 3821 SUP DE PRODUCCION</t>
         </is>
       </c>
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>SENIOR BUSINESS CONTROLLER</t>
+          <t>SUPERVISOR DE PRODUCCIÓN</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -3456,27 +3414,8 @@
       <c r="D16" s="5" t="inlineStr"/>
       <c r="E16" s="5" t="inlineStr"/>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>3010 KITS PRODUCTION - PGS / 3821 SUP DE PRODUCCION</t>
-        </is>
-      </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>SUPERVISOR DE PRODUCCIÓN</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>Elaborar matriz IPERC para el puesto</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr"/>
-      <c r="E17" s="4" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:E17"/>
+  <autoFilter ref="A4:E16"/>
   <mergeCells count="2">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
@@ -3491,7 +3430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -3539,34 +3478,34 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>4207 EHS-SD</t>
+          <t>3120 PLANTA TERMICA PLANTABAL</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>AUXILIAR ADMINISTRATIVO</t>
+          <t>INGENIERO DE CALDERO</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Fuera de alcance - Santo Domingo</t>
+          <t>Cargo operativo</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>No se evalúa en este control</t>
+          <t>Fuera del universo administrativo</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>4507 QUALITY SD</t>
+          <t>4207 EHS-SD</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>TECNICO DE CALIDAD</t>
+          <t>AUXILIAR ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -3576,51 +3515,51 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>No se evalúa en este control</t>
+          <t>No se evalua en este control</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>5007 PGS-CMBA-PRODUCT MANAGER</t>
+          <t>4507 QUALITY SD</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>PRODUCT MANAGER GLOBAL</t>
+          <t>TECNICO DE CALIDAD</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Fuera de alcance - High Point (Product Manager)</t>
+          <t>Fuera de alcance - Santo Domingo</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>No se evalúa en este control</t>
+          <t>No se evalua en este control</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>5033 PGS-CMBA Supply Chain</t>
+          <t>5007 PGS-CMBA-PRODUCT MANAGER</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>ASISTENTE DE COMPRAS</t>
+          <t>PRODUCT MANAGER GLOBAL</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Fuera de alcance - High Point (PGS-CMBA Supply Chain)</t>
+          <t>Fuera de alcance - High Point (Product Manager)</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>No se evalúa en este control</t>
+          <t>No se evalua en este control</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3571,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>JEFE DE LOGISTICA Y PLANIFICACION DE LA DEMANDA</t>
+          <t>ASISTENTE DE COMPRAS</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -3642,56 +3581,78 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>No se evalúa en este control</t>
+          <t>No se evalua en este control</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>5927 PBAL-CMBA-R&amp;D</t>
+          <t>5033 PGS-CMBA Supply Chain</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>JEFE REGIONAL DE LABORATORIO</t>
+          <t>JEFE DE LOGISTICA Y PLANIFICACION DE LA DEMANDA</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Fuera de alcance - High Point (R&amp;D)</t>
+          <t>Fuera de alcance - High Point (PGS-CMBA Supply Chain)</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>No se evalúa en este control</t>
+          <t>No se evalua en este control</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
+          <t>5927 PBAL-CMBA-R&amp;D</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>JEFE REGIONAL DE LABORATORIO</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Fuera de alcance - High Point (R&amp;D)</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>No se evalua en este control</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
           <t>5937 PBAL-CMBA CERTIFICATION MX</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>COORDINADOR ESG</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>Fuera de alcance - High Point (Certification MX)</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>No se evalúa en este control</t>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>No se evalua en este control</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:D11"/>
+  <autoFilter ref="A4:D12"/>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
@@ -3701,214 +3662,6 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>DIFERENCIAS RESPECTO AL CORTE DEL HEAD COUNT V1.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>PLANTACIONES DE BALSA PLANTABAL S.A. / 3A CORE MATERIALS  ·  Control de cobertura IPERC - Personal administrativo  ·  Corte 14/10/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Tipo de cambio</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Cargo</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Acción sugerida</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>BAJA - ya no consta en el head count</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>ANALISTA DE REDES</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Evaluar si corresponde retirar su bloque de la matriz IPERC</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>BAJA - ya no consta en el head count</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>MEDICO OCUPACIONAL</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>Renombrado a MEDICO: sin accion</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>BAJA - ya no consta en el head count</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>MENSAJERO / REPARTIDOR</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Evaluar si corresponde retirar su bloque de la matriz IPERC</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>ALTA - no constaba en el corte anterior</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>AUXILIAR DE SERVICIOS DE SALUD</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>Ya cubierto por matriz</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>ALTA - no constaba en el corte anterior</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>COORDINADOR DE SEGURIDAD FISICA</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Verificar cobertura</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>ALTA - no constaba en el corte anterior</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>INGENIERO DE CALDERO</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>Verificar cobertura</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>ALTA - no constaba en el corte anterior</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>JEFE DE CONTABILIDAD E IMPUESTOS</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>Ya cubierto por matriz</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>ALTA - no constaba en el corte anterior</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>MEDICO</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Ya cubierto por matriz</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>ALTA - no constaba en el corte anterior</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>PEOPLE OPERATIONS PARTNER</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>Ya cubierto por matriz</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A4:C13"/>
-  <mergeCells count="2">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A2:C2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
